--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPJ_DAE_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPJ_DAE_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPJ_DAE_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPJ_DAE_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -268,7 +268,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -624,7 +624,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1324,9 +1324,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>27.51</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>68.37</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>38.02</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>45674</v>
+        <v>45675</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>31.86</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>93.62</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45737</v>
+        <v>45738</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>28.58</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>45801</v>
+        <v>45802</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>54.68</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>13.96</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>12.43</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>1.96</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>93.15000000000001</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>58.48</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45842</v>
+        <v>45843</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>31.62</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>79.58</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>18.41</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>45794</v>
+        <v>45795</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>71.64</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>39.61</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>45906</v>
+        <v>45907</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>26.76</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>47.04</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>85.11</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>3.84</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>47.85</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>2.4</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>15.77</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>8.43</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>75.15000000000001</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45807</v>
+        <v>45808</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44.15</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>36.82</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>70.84</v>
       </c>
       <c r="AI34" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>76.52</v>
       </c>
       <c r="AI35" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>65.81999999999999</v>
       </c>
       <c r="AI36" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>5.55</v>
       </c>
       <c r="AI38" s="5" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>55.11</v>
       </c>
       <c r="AI39" s="5" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>45778</v>
+        <v>45779</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>35.88</v>
       </c>
       <c r="AI40" s="5" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -9102,9 +9102,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -9290,7 +9290,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45592</v>
+        <v>45593</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -9485,7 +9485,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.3854166666666667</v>
@@ -9675,7 +9675,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.40625</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.5520833333333334</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.3020833333333333</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.7083333333333334</v>
@@ -10064,7 +10064,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.96875</v>
@@ -10255,7 +10255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45711</v>
+        <v>45712</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.3125</v>
@@ -10445,7 +10445,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.75</v>
@@ -10644,7 +10644,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.8125</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45816</v>
+        <v>45817</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>0.3541666666666667</v>
@@ -10993,7 +10993,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45920</v>
+        <v>45921</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.2708333333333333</v>
@@ -11025,7 +11025,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.5416666666666666</v>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.34375</v>
@@ -11216,7 +11216,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.6979166666666666</v>
@@ -11403,7 +11403,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.9895833333333334</v>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.4375</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.625</v>
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.5104166666666666</v>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.9166666666666666</v>
@@ -11974,7 +11974,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.3125</v>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45746</v>
+        <v>45747</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.5729166666666666</v>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.9583333333333334</v>
@@ -12356,7 +12356,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -12514,7 +12514,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.65625</v>
@@ -12546,7 +12546,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.65625</v>
@@ -12741,7 +12741,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45927</v>
+        <v>45928</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.7395833333333334</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.34375</v>
@@ -12923,7 +12923,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.3541666666666667</v>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.46875</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>45780</v>
+        <v>45781</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.46875</v>
@@ -13309,7 +13309,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.6666666666666666</v>
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.53125</v>
@@ -13503,7 +13503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.7604166666666666</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -13689,7 +13689,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.3125</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.8020833333333334</v>
@@ -13875,7 +13875,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.9166666666666666</v>
@@ -14034,7 +14034,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -14070,7 +14070,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.7604166666666666</v>
@@ -14261,7 +14261,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>45835</v>
+        <v>45836</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.6354166666666666</v>
@@ -14452,7 +14452,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45786</v>
+        <v>45787</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.5520833333333334</v>
@@ -14647,7 +14647,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.5416666666666666</v>
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.5104166666666666</v>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>0.3854166666666667</v>
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="AD34" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -15186,7 +15186,7 @@
         </is>
       </c>
       <c r="AJ34" s="5" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AK34" s="8" t="n">
         <v>0.7395833333333334</v>
@@ -15214,7 +15214,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>45590</v>
+        <v>45591</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="AD35" s="8" t="n">
         <v>0.875</v>
@@ -15379,7 +15379,7 @@
         </is>
       </c>
       <c r="AJ35" s="5" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="AK35" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="AD36" s="8" t="n">
         <v>0.78125</v>
@@ -15570,7 +15570,7 @@
         </is>
       </c>
       <c r="AJ36" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AK36" s="8" t="n">
         <v>0.4375</v>
@@ -15735,7 +15735,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="AD38" s="8" t="n">
         <v>0.5520833333333334</v>
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="AJ38" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK38" s="8" t="n">
         <v>0.3020833333333333</v>
@@ -15794,7 +15794,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD39" s="8" t="n">
         <v>0.8229166666666666</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="AJ39" s="5" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="AK39" s="8" t="n">
         <v>0.8229166666666666</v>
@@ -15989,7 +15989,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AD40" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="AJ40" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK40" s="8" t="n">
         <v>0.96875</v>
@@ -18174,7 +18174,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18680,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
